--- a/tests/workbooktests/workbooks/test_cashflows.xlsx
+++ b/tests/workbooktests/workbooks/test_cashflows.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740B449C-6DC4-46D2-B089-DAD9080B2F7C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7570770-E35F-4B87-A01B-C898BEECD867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
+    <workbookView xWindow="-4560" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="26" r:id="rId1"/>
@@ -29,6 +29,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -36,8 +47,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="213">
   <si>
     <t>evaluationDate</t>
   </si>
@@ -661,13 +694,28 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>=qlCashFlowsNpv(B20;B4;WAHR)</t>
+  </si>
+  <si>
+    <t>=qlCashFlowsBps(B20;B4;WAHR)</t>
+  </si>
+  <si>
+    <t>=qlCashFlowsNpv(B20#;B4;WAHR)</t>
+  </si>
+  <si>
+    <t>=qlCashFlowsBps(B20#;B4;WAHR)</t>
+  </si>
+  <si>
+    <t>=qlCashFlowsNpvBps(B20#;B4;WAHR)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -990,7 +1038,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1121,6 +1169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1456,15 +1505,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651A84EC-9A2D-4A83-BADE-B9CC686F0550}">
   <dimension ref="B1:L30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="18.375" style="41" customWidth="1"/>
-    <col min="12" max="12" width="19.375" style="41" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="18.42578125" style="41" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" style="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1"/>
-    <row r="2" spans="2:12" ht="30">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
         <v>205</v>
       </c>
@@ -1481,7 +1530,7 @@
       <c r="K2" s="44"/>
       <c r="L2" s="45"/>
     </row>
-    <row r="3" spans="2:12" ht="45.75" thickBot="1">
+    <row r="3" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="46"/>
       <c r="C3" s="47" t="s">
         <v>192</v>
@@ -1514,7 +1563,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="49" t="s">
         <v>203</v>
       </c>
@@ -1529,7 +1578,7 @@
       <c r="K4" s="54"/>
       <c r="L4" s="55"/>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="50" t="s">
         <v>193</v>
       </c>
@@ -1544,7 +1593,7 @@
       <c r="K5" s="57"/>
       <c r="L5" s="58"/>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="50" t="s">
         <v>204</v>
       </c>
@@ -1559,7 +1608,7 @@
       <c r="K6" s="57"/>
       <c r="L6" s="58"/>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="51" t="s">
         <v>168</v>
       </c>
@@ -1574,7 +1623,7 @@
       <c r="K7" s="57"/>
       <c r="L7" s="58"/>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="50" t="s">
         <v>169</v>
       </c>
@@ -1589,7 +1638,7 @@
       <c r="K8" s="57"/>
       <c r="L8" s="58"/>
     </row>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="51" t="s">
         <v>170</v>
       </c>
@@ -1604,7 +1653,7 @@
       <c r="K9" s="57"/>
       <c r="L9" s="58"/>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="50" t="s">
         <v>171</v>
       </c>
@@ -1621,7 +1670,7 @@
       <c r="K10" s="57"/>
       <c r="L10" s="58"/>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="50" t="s">
         <v>172</v>
       </c>
@@ -1638,7 +1687,7 @@
       <c r="K11" s="57"/>
       <c r="L11" s="58"/>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="51" t="s">
         <v>173</v>
       </c>
@@ -1653,7 +1702,7 @@
       <c r="K12" s="57"/>
       <c r="L12" s="58"/>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="50" t="s">
         <v>174</v>
       </c>
@@ -1670,7 +1719,7 @@
       <c r="K13" s="57"/>
       <c r="L13" s="58"/>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="51" t="s">
         <v>178</v>
       </c>
@@ -1685,7 +1734,7 @@
       <c r="K14" s="57"/>
       <c r="L14" s="58"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="50" t="s">
         <v>175</v>
       </c>
@@ -1702,7 +1751,7 @@
       </c>
       <c r="L15" s="58"/>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="51" t="s">
         <v>176</v>
       </c>
@@ -1717,7 +1766,7 @@
       <c r="K16" s="57"/>
       <c r="L16" s="58"/>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="51" t="s">
         <v>177</v>
       </c>
@@ -1732,7 +1781,7 @@
       <c r="K17" s="57"/>
       <c r="L17" s="58"/>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="51" t="s">
         <v>179</v>
       </c>
@@ -1747,7 +1796,7 @@
       <c r="K18" s="57"/>
       <c r="L18" s="58"/>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="51" t="s">
         <v>180</v>
       </c>
@@ -1762,7 +1811,7 @@
       <c r="K19" s="57"/>
       <c r="L19" s="58"/>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="51" t="s">
         <v>181</v>
       </c>
@@ -1777,7 +1826,7 @@
       <c r="K20" s="57"/>
       <c r="L20" s="58"/>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="51" t="s">
         <v>182</v>
       </c>
@@ -1792,7 +1841,7 @@
       <c r="K21" s="57"/>
       <c r="L21" s="58"/>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
         <v>183</v>
       </c>
@@ -1807,7 +1856,7 @@
       <c r="K22" s="57"/>
       <c r="L22" s="58"/>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="51" t="s">
         <v>184</v>
       </c>
@@ -1822,7 +1871,7 @@
       <c r="K23" s="57"/>
       <c r="L23" s="58"/>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="51" t="s">
         <v>185</v>
       </c>
@@ -1837,7 +1886,7 @@
       <c r="K24" s="57"/>
       <c r="L24" s="58"/>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="51" t="s">
         <v>186</v>
       </c>
@@ -1852,7 +1901,7 @@
       <c r="K25" s="57"/>
       <c r="L25" s="58"/>
     </row>
-    <row r="26" spans="2:12">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="51" t="s">
         <v>187</v>
       </c>
@@ -1867,7 +1916,7 @@
       <c r="K26" s="57"/>
       <c r="L26" s="58"/>
     </row>
-    <row r="27" spans="2:12">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="51" t="s">
         <v>188</v>
       </c>
@@ -1882,7 +1931,7 @@
       <c r="K27" s="57"/>
       <c r="L27" s="58"/>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="51" t="s">
         <v>189</v>
       </c>
@@ -1897,7 +1946,7 @@
       <c r="K28" s="57"/>
       <c r="L28" s="58"/>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="51" t="s">
         <v>190</v>
       </c>
@@ -1912,7 +1961,7 @@
       <c r="K29" s="57"/>
       <c r="L29" s="58"/>
     </row>
-    <row r="30" spans="2:12" ht="15" thickBot="1">
+    <row r="30" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="52" t="s">
         <v>191</v>
       </c>
@@ -1936,14 +1985,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F330C7E-B571-4B08-A212-8E2A0B8B7A63}">
   <dimension ref="A1:C56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="73" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>125</v>
       </c>
@@ -1951,7 +2000,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1960,7 +2009,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>111</v>
       </c>
@@ -1971,7 +2020,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>16</v>
       </c>
@@ -1982,7 +2031,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>112</v>
       </c>
@@ -1993,7 +2042,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>113</v>
       </c>
@@ -2004,7 +2053,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>114</v>
       </c>
@@ -2015,7 +2064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>124</v>
       </c>
@@ -2028,7 +2077,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R9C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>150</v>
       </c>
@@ -2041,7 +2090,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R10C3Euribor,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>149</v>
       </c>
@@ -2054,7 +2103,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R11C3Euribor,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
         <v>151</v>
       </c>
@@ -2067,7 +2116,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R12C3SwapIndex,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
         <v>152</v>
       </c>
@@ -2080,7 +2129,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R13C3SwapIndex,A</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>148</v>
       </c>
@@ -2093,7 +2142,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R14C3SwapSpreadIndex,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>116</v>
       </c>
@@ -2102,7 +2151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>117</v>
       </c>
@@ -2111,7 +2160,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>118</v>
       </c>
@@ -2120,7 +2169,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>119</v>
       </c>
@@ -2129,7 +2178,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>120</v>
       </c>
@@ -2138,7 +2187,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>121</v>
       </c>
@@ -2147,7 +2196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>130</v>
       </c>
@@ -2156,7 +2205,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>123</v>
       </c>
@@ -2165,7 +2214,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
         <v>147</v>
       </c>
@@ -2178,7 +2227,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R23C3CmsSpreadCoupon,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>153</v>
       </c>
@@ -2191,7 +2240,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R24C3SwaptionVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>154</v>
       </c>
@@ -2202,7 +2251,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
         <v>155</v>
       </c>
@@ -2213,7 +2262,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
         <v>159</v>
       </c>
@@ -2226,7 +2275,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R27C3AnalyticHaganPricer,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="39" t="s">
         <v>162</v>
       </c>
@@ -2237,7 +2286,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="36" t="s">
         <v>161</v>
       </c>
@@ -2250,7 +2299,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R29C3LognormalCmsSpreadPricer,A</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
         <v>132</v>
       </c>
@@ -2263,7 +2312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>61</v>
       </c>
@@ -2276,7 +2325,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
         <v>62</v>
       </c>
@@ -2289,7 +2338,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
         <v>63</v>
       </c>
@@ -2302,7 +2351,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
         <v>64</v>
       </c>
@@ -2315,7 +2364,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
         <v>65</v>
       </c>
@@ -2328,7 +2377,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
         <v>66</v>
       </c>
@@ -2341,7 +2390,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>67</v>
       </c>
@@ -2354,7 +2403,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
         <v>68</v>
       </c>
@@ -2367,7 +2416,7 @@
         <v>0.49863013698630138</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
         <v>69</v>
       </c>
@@ -2380,7 +2429,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
         <v>70</v>
       </c>
@@ -2393,7 +2442,7 @@
         <v>Actual/365 (Fixed)</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
         <v>71</v>
       </c>
@@ -2406,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
         <v>72</v>
       </c>
@@ -2419,7 +2468,7 @@
         <v>45288</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
         <v>73</v>
       </c>
@@ -2432,7 +2481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
         <v>129</v>
       </c>
@@ -2445,7 +2494,7 @@
         <v>FOLLOWING</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
         <v>74</v>
       </c>
@@ -2458,7 +2507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
         <v>75</v>
       </c>
@@ -2471,7 +2520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>76</v>
       </c>
@@ -2484,7 +2533,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
         <v>77</v>
       </c>
@@ -2497,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
         <v>78</v>
       </c>
@@ -2510,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="24" t="s">
         <v>79</v>
       </c>
@@ -2523,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="30" t="s">
         <v>124</v>
       </c>
@@ -2536,7 +2585,7 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R51C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
         <v>80</v>
       </c>
@@ -2549,7 +2598,7 @@
         <v>4.936822095803213E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
         <v>81</v>
       </c>
@@ -2562,12 +2611,12 @@
         <v>欣[test_cashflows.xlsx]CmsSpreadCoupon!R53C3InterestRateIndex,A</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="38" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="38" t="s">
         <v>164</v>
       </c>
@@ -2580,13 +2629,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE44A8B2-F254-4D98-B6A0-E677E4F5C119}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2594,7 +2643,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2611,16 +2660,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F75C3A2-660E-4D76-B179-F0DF6BFBAF45}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.125" customWidth="1"/>
-    <col min="2" max="2" width="60.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="24.875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="60.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -2629,7 +2678,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2638,7 +2687,7 @@
         <v>欣[test_cashflows.xlsx]CashFlows!R3C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2647,7 +2696,7 @@
         <v>欣[test_cashflows.xlsx]CashFlows!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2656,7 +2705,7 @@
         <v>欣[test_cashflows.xlsx]CashFlows!R5C2EquityIndex,A</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2665,7 +2714,7 @@
         <v>46511</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2673,10 +2722,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>10</v>
       </c>
@@ -2687,7 +2736,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2708,7 +2757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2729,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -2750,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2772,7 +2821,7 @@
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2789,15 +2838,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CD6594-2B3F-411B-9C55-7B2A9E18A8AB}">
   <dimension ref="A1:BP83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="68" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="68" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -2806,7 +2855,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2815,7 +2864,7 @@
         <v>欣[test_cashflows.xlsx]Coupons!R3C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2824,7 +2873,7 @@
         <v>欣[test_cashflows.xlsx]Coupons!R5C2Eonia,A</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2833,7 +2882,7 @@
         <v>欣[test_cashflows.xlsx]Coupons!R6C2Euribor,A</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2841,7 +2890,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2849,7 +2898,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2857,7 +2906,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2865,7 +2914,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2873,7 +2922,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2882,7 +2931,7 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2891,7 +2940,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2900,7 +2949,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -2909,7 +2958,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2918,7 +2967,7 @@
         <v>欣[test_cashflows.xlsx]Coupons!R18C2Schedule,A</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2935,7 +2984,7 @@
         <v>0.76666666666667105</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2952,7 +3001,7 @@
         <v>0.75903052613170985</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -2969,7 +3018,7 @@
         <v>0.75903052613170985</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -2986,7 +3035,7 @@
         <v>0.75622180895558166</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -3003,7 +3052,7 @@
         <v>0.75902068142262313</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3016,7 +3065,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>84</v>
       </c>
@@ -3029,7 +3078,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -3038,7 +3087,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -3047,7 +3096,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -3056,7 +3105,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -3065,7 +3114,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -3074,7 +3123,7 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -3083,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -3092,7 +3141,7 @@
         <v>2.9701194500806039E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -3101,7 +3150,7 @@
         <v>0.25555555555555554</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -3110,7 +3159,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -3119,7 +3168,7 @@
         <v>Actual/360</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -3128,7 +3177,7 @@
         <v>8.2503318057794553E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>72</v>
       </c>
@@ -3137,7 +3186,7 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>73</v>
       </c>
@@ -3146,7 +3195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -3155,7 +3204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>75</v>
       </c>
@@ -3164,7 +3213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>76</v>
       </c>
@@ -3173,7 +3222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>77</v>
       </c>
@@ -3182,7 +3231,7 @@
         <v>2.9701194500806039E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>78</v>
       </c>
@@ -3191,7 +3240,7 @@
         <v>2.9701194500806039E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>79</v>
       </c>
@@ -3200,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>80</v>
       </c>
@@ -3209,7 +3258,7 @@
         <v>0.74751496433099018</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>81</v>
       </c>
@@ -3218,7 +3267,7 @@
         <v>欣[test_cashflows.xlsx]Coupons!R49C2InterestRateIndex,A</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -3227,7 +3276,7 @@
         <v>Euribor3M Actual/360</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>83</v>
       </c>
@@ -3236,13 +3285,13 @@
         <v>欣[test_cashflows.xlsx]Coupons!R51C2BlackIborCouponPricer,A</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="b">
         <f t="array" ref="B52">_xll.qlFloatingRateCouponSetPricer(B21,B51)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>85</v>
       </c>
@@ -3251,7 +3300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -3260,7 +3309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -3269,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>87</v>
       </c>
@@ -3278,7 +3327,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -3287,7 +3336,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>89</v>
       </c>
@@ -3296,7 +3345,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -3305,7 +3354,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>91</v>
       </c>
@@ -3314,7 +3363,7 @@
         <v>COMPOUND</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -3323,7 +3372,7 @@
         <v>SIMPLE</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -3332,7 +3381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:68">
+    <row r="65" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -3341,7 +3390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:68">
+    <row r="66" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -3350,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:68">
+    <row r="67" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -3359,7 +3408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:68">
+    <row r="68" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -3368,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:68">
+    <row r="69" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -3377,11 +3426,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:68">
+    <row r="70" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>98</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="1" cm="1">
         <f t="array" ref="B70:BP70">TRANSPOSE(_xll.qlOvernightIndexedCouponValueDates(B22))</f>
         <v>46240</v>
       </c>
@@ -3584,11 +3633,11 @@
         <v>46332</v>
       </c>
     </row>
-    <row r="71" spans="1:68">
+    <row r="71" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>99</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="1" cm="1">
         <f t="array" ref="B71:BO71">TRANSPOSE(_xll.qlOvernightIndexedCouponFixingDates(B22))</f>
         <v>46240</v>
       </c>
@@ -3789,11 +3838,11 @@
       </c>
       <c r="BP71" s="1"/>
     </row>
-    <row r="72" spans="1:68">
+    <row r="72" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>100</v>
       </c>
-      <c r="B72">
+      <c r="B72" cm="1">
         <f t="array" ref="B72:BO72">TRANSPOSE(_xll.qlOvernightIndexedCouponDt(B22))</f>
         <v>2.7777777777777779E-3</v>
       </c>
@@ -3993,11 +4042,11 @@
         <v>2.7777777777777779E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:68">
+    <row r="73" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>101</v>
       </c>
-      <c r="B73">
+      <c r="B73" cm="1">
         <f t="array" ref="B73:BO73">TRANSPOSE(_xll.qlOvernightIndexedCouponIndexFixings(B22))</f>
         <v>2.9590257117293461E-2</v>
       </c>
@@ -4197,7 +4246,7 @@
         <v>2.9590257117213525E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:68">
+    <row r="74" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -4206,7 +4255,7 @@
         <v>2.9701194500806039E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:68">
+    <row r="75" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -4215,7 +4264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:68">
+    <row r="77" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -4224,7 +4273,7 @@
         <v>欣[test_cashflows.xlsx]Coupons!R77C2OvernightIndexedCoupon,A</v>
       </c>
     </row>
-    <row r="78" spans="1:68">
+    <row r="78" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>105</v>
       </c>
@@ -4233,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:68">
+    <row r="79" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>106</v>
       </c>
@@ -4242,7 +4291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:68">
+    <row r="80" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -4251,7 +4300,7 @@
         <v>COMPOUND</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>108</v>
       </c>
@@ -4260,7 +4309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -4269,7 +4318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -4285,16 +4334,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33350399-A1BE-49BB-B0E5-3B8BD9C2C423}">
-  <dimension ref="A1:I33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="39.25" customWidth="1"/>
-    <col min="6" max="6" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -4303,7 +4352,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4318,7 +4367,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4326,12 +4375,12 @@
         <f>_xll.qlFlatForward(B1,0.02,"actual365fixed","Continuous")</f>
         <v>欣[test_cashflows.xlsx]Legs!R4C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="1" cm="1">
         <f t="array" ref="F4:F12">_xll.qlScheduleDates(B18)</f>
         <v>46238</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F5" s="1">
         <v>46330</v>
       </c>
@@ -4342,7 +4391,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4361,7 +4410,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -4377,7 +4426,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -4393,7 +4442,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -4409,7 +4458,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -4425,7 +4474,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F11" s="1">
         <v>46877</v>
       </c>
@@ -4434,7 +4483,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -4449,7 +4498,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -4458,7 +4507,7 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -4467,7 +4516,7 @@
         <v>46969</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -4475,7 +4524,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -4483,7 +4532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -4491,424 +4540,255 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
       <c r="B18" t="str">
         <f t="array" ref="B18">_xll.qlMakeSchedule(B13,B14,B15,,B12,B16)</f>
-        <v>欣[test_cashflows.xlsx]Legs!R18C2Schedule,A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>欣[test_cashflows.xlsx]Legs!R18C2Schedule,C</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="5" t="str">
+      <c r="B20" s="5" t="str" cm="1">
         <f t="array" ref="B20:I20">TRANSPOSE(_xll.qlFixedRateLeg(B18,B17,G5:G12,I5:I6))</f>
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,A</v>
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,A</v>
       </c>
       <c r="C20" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,B</v>
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,B</v>
       </c>
       <c r="D20" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,C</v>
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,C</v>
       </c>
       <c r="E20" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,D</v>
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,D</v>
       </c>
       <c r="F20" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,E</v>
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,E</v>
       </c>
       <c r="G20" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,F</v>
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,F</v>
       </c>
       <c r="H20" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,G</v>
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,G</v>
       </c>
       <c r="I20" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R20C2:R20C9CashFlow,H</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>欣[test_cashflows.xlsx]Legs!R20C2CashFlow,H</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="5" t="str">
+      <c r="B21" s="5" t="str" cm="1">
         <f t="array" ref="B21:I21">TRANSPOSE(_xll.qlIborLeg(G5,B18,B7,,,4))</f>
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,A</v>
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,A</v>
       </c>
       <c r="C21" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,B</v>
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,B</v>
       </c>
       <c r="D21" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,C</v>
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,C</v>
       </c>
       <c r="E21" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,D</v>
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,D</v>
       </c>
       <c r="F21" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,E</v>
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,E</v>
       </c>
       <c r="G21" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,F</v>
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,F</v>
       </c>
       <c r="H21" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,G</v>
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,G</v>
       </c>
       <c r="I21" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R21C2:R21C9CashFlow,H</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>欣[test_cashflows.xlsx]Legs!R21C2CashFlow,H</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="5" t="str">
+      <c r="B22" s="5" t="str" cm="1">
         <f t="array" ref="B22:I22">TRANSPOSE(_xll.qlOvernightLeg(G5,B18,B6))</f>
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,A</v>
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,A</v>
       </c>
       <c r="C22" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,B</v>
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,B</v>
       </c>
       <c r="D22" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,C</v>
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,C</v>
       </c>
       <c r="E22" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,D</v>
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,D</v>
       </c>
       <c r="F22" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,E</v>
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,E</v>
       </c>
       <c r="G22" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,F</v>
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,F</v>
       </c>
       <c r="H22" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,G</v>
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,G</v>
       </c>
       <c r="I22" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R22C2:R22C9CashFlow,H</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>欣[test_cashflows.xlsx]Legs!R22C2CashFlow,H</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="5" t="str">
+      <c r="B23" s="5" t="str" cm="1">
         <f t="array" ref="B23:I23">TRANSPOSE(_xll.qlCmsLeg(G5,B18,B8))</f>
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,A</v>
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,A</v>
       </c>
       <c r="C23" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,B</v>
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,B</v>
       </c>
       <c r="D23" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,C</v>
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,C</v>
       </c>
       <c r="E23" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,D</v>
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,D</v>
       </c>
       <c r="F23" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,E</v>
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,E</v>
       </c>
       <c r="G23" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,F</v>
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,F</v>
       </c>
       <c r="H23" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,G</v>
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,G</v>
       </c>
       <c r="I23" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R23C2:R23C9CashFlow,H</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>欣[test_cashflows.xlsx]Legs!R23C2CashFlow,H</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="5" t="e">
-        <f t="array" ref="B24:I24">TRANSPOSE(_xll.qlCmsZeroLeg(G5,B18,B9))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" s="5" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D24" s="5" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E24" s="5" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F24" s="5" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G24" s="5" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H24" s="5" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I24" s="5" t="e">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="B24" s="5" t="str" cm="1">
+        <f t="array" ref="B24:I24">TRANSPOSE(_xll.qlCmsZeroLeg(G5,B18,B9,,,,,,,,,"TARGET"))</f>
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,A</v>
+      </c>
+      <c r="C24" s="5" t="str">
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,B</v>
+      </c>
+      <c r="D24" s="5" t="str">
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,C</v>
+      </c>
+      <c r="E24" s="5" t="str">
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,D</v>
+      </c>
+      <c r="F24" s="5" t="str">
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,E</v>
+      </c>
+      <c r="G24" s="5" t="str">
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,F</v>
+      </c>
+      <c r="H24" s="5" t="str">
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,G</v>
+      </c>
+      <c r="I24" s="5" t="str">
+        <v>欣[test_cashflows.xlsx]Legs!R24C2CashFlow,H</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="5" t="str">
+      <c r="B25" s="5" t="str" cm="1">
         <f t="array" ref="B25:I25">TRANSPOSE(_xll.qlCmsSpreadLeg(G5:G7,B18,B10))</f>
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,A</v>
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,A</v>
       </c>
       <c r="C25" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,B</v>
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,B</v>
       </c>
       <c r="D25" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,C</v>
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,C</v>
       </c>
       <c r="E25" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,D</v>
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,D</v>
       </c>
       <c r="F25" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,E</v>
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,E</v>
       </c>
       <c r="G25" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,F</v>
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,F</v>
       </c>
       <c r="H25" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,G</v>
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,G</v>
       </c>
       <c r="I25" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R25C2:R25C9CashFlow,H</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>欣[test_cashflows.xlsx]Legs!R25C2CashFlow,H</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="5" t="str">
+      <c r="B26" s="5" t="str" cm="1">
         <f t="array" ref="B26:E26">TRANSPOSE(_xll.qlMultipleResetsLeg(B18,B7,2,G5))</f>
-        <v>欣[test_cashflows.xlsx]Legs!R26C2:R26C5CashFlow,A</v>
+        <v>欣[test_cashflows.xlsx]Legs!R26C2CashFlow,A</v>
       </c>
       <c r="C26" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R26C2:R26C5CashFlow,B</v>
+        <v>欣[test_cashflows.xlsx]Legs!R26C2CashFlow,B</v>
       </c>
       <c r="D26" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R26C2:R26C5CashFlow,C</v>
+        <v>欣[test_cashflows.xlsx]Legs!R26C2CashFlow,C</v>
       </c>
       <c r="E26" s="5" t="str">
-        <v>欣[test_cashflows.xlsx]Legs!R26C2:R26C5CashFlow,D</v>
+        <v>欣[test_cashflows.xlsx]Legs!R26C2CashFlow,D</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>56</v>
       </c>
-      <c r="B28">
-        <f t="array" ref="B28">_xll.qlCashFlowsNpv(B20,B4,TRUE)</f>
-        <v>0.75897582173628064</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="B28" s="62" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>57</v>
       </c>
-      <c r="B29">
-        <f t="array" ref="B29">_xll.qlCashFlowsBps(B20,B4,TRUE)</f>
-        <v>2.5299194057875878E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="B29" s="62" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
-      <c r="B30" t="str">
-        <f t="array" aca="1" ref="B30" ca="1">_xll.qlCashFlowsNpv(_xlfn.ANCHORARRAY(B20),B4,TRUE)</f>
-        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_npv'.
-  Possible C/C++ prototypes are:
-    CashFlows::npv(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::npv(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-    CashFlows::npv(Leg const &amp;,InterestRate const &amp;,bool,Date,Date)
-    CashFlows::npv(Leg const &amp;,InterestRate const &amp;,bool,Date)
-    CashFlows::npv(Leg const &amp;,InterestRate const &amp;,bool)
-    CashFlows::npv(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date,Date)
-    CashFlows::npv(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date)
-    CashFlows::npv(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency,ext::optional&lt; bool &gt;,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency,ext::optional&lt; bool &gt;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency,ext::optional&lt; bool &gt;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,DayCounter const &amp;,Compounding,Frequency,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,DayCounter const &amp;,Compounding,Frequency,bool,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,DayCounter const &amp;,Compounding,Frequency,bool)
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\cashflows.py", line 3168, in qlCashFlowsNpv
-    return ql.CashFlows.npv(
-           ~~~~~~~~~~~~~~~~^
-        to_object_list(leg, ql.CashFlow),
-        ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-    ...&lt;3 lines&gt;...
-        npv_date,
-        ^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\.conda\envs\qlxloil\Lib\site-packages\QuantLib\QuantLib.py", line 15299, in npv
-    return _QuantLib.CashFlows_npv(*args)
-           ~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^
-TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_npv'.
-  Possible C/C++ prototypes are:
-    CashFlows::npv(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::npv(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-    CashFlows::npv(Leg const &amp;,InterestRate const &amp;,bool,Date,Date)
-    CashFlows::npv(Leg const &amp;,InterestRate const &amp;,bool,Date)
-    CashFlows::npv(Leg const &amp;,InterestRate const &amp;,bool)
-    CashFlows::npv(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date,Date)
-    CashFlows::npv(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date)
-    CashFlows::npv(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency,ext::optional&lt; bool &gt;,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency,ext::optional&lt; bool &gt;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency,ext::optional&lt; bool &gt;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,Compounding,Frequency)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,DayCounter const &amp;,Compounding,Frequency,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,DayCounter const &amp;,Compounding,Frequency,bool,Date const &amp;)
-    CashFlows::npv(Leg const &amp;,ext::shared_ptr&lt; YieldTermStructure &gt; const &amp;,Spread,DayCounter const &amp;,Compounding,Frequency,bool)
-</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="B30" s="62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>59</v>
       </c>
-      <c r="B31" t="str">
-        <f t="array" aca="1" ref="B31" ca="1">_xll.qlCashFlowsBps(_xlfn.ANCHORARRAY(B20),B4,TRUE)</f>
-        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_bps'.
-  Possible C/C++ prototypes are:
-    CashFlows::bps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::bps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-    CashFlows::bps(Leg const &amp;,InterestRate const &amp;,bool,Date,Date)
-    CashFlows::bps(Leg const &amp;,InterestRate const &amp;,bool,Date)
-    CashFlows::bps(Leg const &amp;,InterestRate const &amp;,bool)
-    CashFlows::bps(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date,Date)
-    CashFlows::bps(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date)
-    CashFlows::bps(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool)
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\cashflows.py", line 3301, in qlCashFlowsBps
-    return ql.CashFlows.bps(
-           ~~~~~~~~~~~~~~~~^
-        to_object_list(leg, ql.CashFlow),
-        ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-    ...&lt;3 lines&gt;...
-        npv_date,
-        ^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\.conda\envs\qlxloil\Lib\site-packages\QuantLib\QuantLib.py", line 15309, in bps
-    return _QuantLib.CashFlows_bps(*args)
-           ~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^
-TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_bps'.
-  Possible C/C++ prototypes are:
-    CashFlows::bps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::bps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::bps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-    CashFlows::bps(Leg const &amp;,InterestRate const &amp;,bool,Date,Date)
-    CashFlows::bps(Leg const &amp;,InterestRate const &amp;,bool,Date)
-    CashFlows::bps(Leg const &amp;,InterestRate const &amp;,bool)
-    CashFlows::bps(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date,Date)
-    CashFlows::bps(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool,Date)
-    CashFlows::bps(Leg const &amp;,Rate,DayCounter const &amp;,Compounding,Frequency,bool)
-</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="B31" s="62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>60</v>
       </c>
-      <c r="B32" t="str">
-        <f t="array" aca="1" ref="B32:B33" ca="1">_xll.qlCashFlowsNpvBps(_xlfn.ANCHORARRAY(B20),B4,TRUE)</f>
-        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_npvbps'.
-  Possible C/C++ prototypes are:
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::CashFlows_npvbps__SWIG_3(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\cashflows.py", line 3394, in qlCashFlowsNpvBps
-    npv, bps = ql.CashFlows.npvbps(
-               ~~~~~~~~~~~~~~~~~~~^
-        to_object_list(leg, ql.CashFlow),
-        ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-    ...&lt;3 lines&gt;...
-        npv_date,
-        ^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\.conda\envs\qlxloil\Lib\site-packages\QuantLib\QuantLib.py", line 15317, in npvbps
-    return _QuantLib.CashFlows_npvbps(*args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^
-TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_npvbps'.
-  Possible C/C++ prototypes are:
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::CashFlows_npvbps__SWIG_3(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_npvbps'.
-  Possible C/C++ prototypes are:
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::CashFlows_npvbps__SWIG_3(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\cashflows.py", line 3394, in qlCashFlowsNpvBps
-    npv, bps = ql.CashFlows.npvbps(
-               ~~~~~~~~~~~~~~~~~~~^
-        to_object_list(leg, ql.CashFlow),
-        ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-    ...&lt;3 lines&gt;...
-        npv_date,
-        ^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\.conda\envs\qlxloil\Lib\site-packages\QuantLib\QuantLib.py", line 15317, in npvbps
-    return _QuantLib.CashFlows_npvbps(*args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^
-TypeError: Wrong number or type of arguments for overloaded function 'CashFlows_npvbps'.
-  Possible C/C++ prototypes are:
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,YieldTermStructure const &amp;,bool)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;,Date const &amp;)
-    CashFlows::npvbps(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool,Date const &amp;)
-    CashFlows::CashFlows_npvbps__SWIG_3(Leg const &amp;,Handle&lt; YieldTermStructure &gt; const &amp;,bool)
-</v>
+      <c r="B32" s="62" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4919,14 +4799,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96807CC9-AEF0-4A4C-9951-6D8BCB14E3D2}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>125</v>
       </c>
@@ -4934,7 +4814,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -4943,7 +4823,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>111</v>
       </c>
@@ -4954,7 +4834,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>16</v>
       </c>
@@ -4965,7 +4845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>112</v>
       </c>
@@ -4976,7 +4856,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>113</v>
       </c>
@@ -4987,7 +4867,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>114</v>
       </c>
@@ -4998,7 +4878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>124</v>
       </c>
@@ -5011,7 +4891,7 @@
         <v>欣[test_cashflows.xlsx]IborCoupon!R9C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>115</v>
       </c>
@@ -5024,7 +4904,7 @@
         <v>欣[test_cashflows.xlsx]IborCoupon!R10C3Euribor,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>116</v>
       </c>
@@ -5033,7 +4913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>117</v>
       </c>
@@ -5042,7 +4922,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>118</v>
       </c>
@@ -5051,7 +4931,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>119</v>
       </c>
@@ -5060,7 +4940,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>120</v>
       </c>
@@ -5069,7 +4949,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>121</v>
       </c>
@@ -5078,7 +4958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>122</v>
       </c>
@@ -5087,7 +4967,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>123</v>
       </c>
@@ -5096,7 +4976,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
         <v>28</v>
       </c>
@@ -5109,7 +4989,7 @@
         <v>欣[test_cashflows.xlsx]IborCoupon!R19C3IborCoupon,A</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
         <v>61</v>
       </c>
@@ -5122,7 +5002,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>62</v>
       </c>
@@ -5135,7 +5015,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
         <v>63</v>
       </c>
@@ -5148,7 +5028,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
         <v>64</v>
       </c>
@@ -5161,7 +5041,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
         <v>65</v>
       </c>
@@ -5174,7 +5054,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
         <v>66</v>
       </c>
@@ -5187,7 +5067,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
         <v>67</v>
       </c>
@@ -5200,7 +5080,7 @@
         <v>2.0825803230683254E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
         <v>68</v>
       </c>
@@ -5213,7 +5093,7 @@
         <v>0.50410958904109593</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
         <v>69</v>
       </c>
@@ -5226,7 +5106,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
         <v>70</v>
       </c>
@@ -5239,7 +5119,7 @@
         <v>Actual/365 (Fixed)</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
         <v>71</v>
       </c>
@@ -5252,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
         <v>72</v>
       </c>
@@ -5265,7 +5145,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>73</v>
       </c>
@@ -5278,7 +5158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
         <v>129</v>
       </c>
@@ -5291,7 +5171,7 @@
         <v>FOLLOWING</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>74</v>
       </c>
@@ -5304,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
         <v>75</v>
       </c>
@@ -5317,7 +5197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
         <v>76</v>
       </c>
@@ -5330,7 +5210,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
         <v>77</v>
       </c>
@@ -5343,7 +5223,7 @@
         <v>1.9825803230683253E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>78</v>
       </c>
@@ -5356,7 +5236,7 @@
         <v>1.9825803230683253E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="24" t="s">
         <v>79</v>
       </c>
@@ -5369,7 +5249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="30" t="s">
         <v>124</v>
       </c>
@@ -5382,7 +5262,7 @@
         <v>欣[test_cashflows.xlsx]IborCoupon!R40C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
         <v>80</v>
       </c>
@@ -5395,7 +5275,7 @@
         <v>1.0290039281841983</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
         <v>81</v>
       </c>
@@ -5416,14 +5296,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D29259-FAC1-4E17-BD03-57F889346F6F}">
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="73" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="78.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="78.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>125</v>
       </c>
@@ -5431,7 +5311,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -5440,7 +5320,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>111</v>
       </c>
@@ -5451,7 +5331,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>16</v>
       </c>
@@ -5462,7 +5342,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>112</v>
       </c>
@@ -5473,7 +5353,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>113</v>
       </c>
@@ -5484,7 +5364,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>114</v>
       </c>
@@ -5495,7 +5375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>124</v>
       </c>
@@ -5508,7 +5388,7 @@
         <v>欣[test_cashflows.xlsx]CappedFlooredIborCoupon!R9C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>115</v>
       </c>
@@ -5521,7 +5401,7 @@
         <v>欣[test_cashflows.xlsx]CappedFlooredIborCoupon!R10C3Euribor,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>116</v>
       </c>
@@ -5530,7 +5410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>117</v>
       </c>
@@ -5539,7 +5419,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>30</v>
       </c>
@@ -5548,7 +5428,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>31</v>
       </c>
@@ -5557,7 +5437,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>118</v>
       </c>
@@ -5566,7 +5446,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>119</v>
       </c>
@@ -5575,7 +5455,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>120</v>
       </c>
@@ -5584,7 +5464,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>121</v>
       </c>
@@ -5593,7 +5473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>130</v>
       </c>
@@ -5602,7 +5482,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
         <v>32</v>
       </c>
@@ -5615,7 +5495,7 @@
         <v>欣[test_cashflows.xlsx]CappedFlooredIborCoupon!R20C3CappedFlooredIborCoupon,A</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
         <v>133</v>
       </c>
@@ -5625,7 +5505,7 @@
         <v>欣[test_cashflows.xlsx]CappedFlooredIborCoupon!R21C3OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
         <v>131</v>
       </c>
@@ -5638,7 +5518,7 @@
         <v>欣[test_cashflows.xlsx]CappedFlooredIborCoupon!R22C3BlackIborCouponPricer,A</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
         <v>132</v>
       </c>
@@ -5651,7 +5531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
         <v>61</v>
       </c>
@@ -5664,7 +5544,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
         <v>62</v>
       </c>
@@ -5677,7 +5557,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
         <v>63</v>
       </c>
@@ -5690,7 +5570,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
         <v>64</v>
       </c>
@@ -5703,7 +5583,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
         <v>65</v>
       </c>
@@ -5716,7 +5596,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
         <v>66</v>
       </c>
@@ -5729,7 +5609,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
         <v>67</v>
       </c>
@@ -5742,7 +5622,7 @@
         <v>2.0825803233769129E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
         <v>68</v>
       </c>
@@ -5755,7 +5635,7 @@
         <v>0.50410958904109593</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>69</v>
       </c>
@@ -5768,7 +5648,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
         <v>70</v>
       </c>
@@ -5781,7 +5661,7 @@
         <v>Actual/365 (Fixed)</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>71</v>
       </c>
@@ -5794,7 +5674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
         <v>72</v>
       </c>
@@ -5807,7 +5687,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
         <v>73</v>
       </c>
@@ -5820,7 +5700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
         <v>129</v>
       </c>
@@ -5833,7 +5713,7 @@
         <v>PRECEDING</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>74</v>
       </c>
@@ -5846,7 +5726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="24" t="s">
         <v>75</v>
       </c>
@@ -5859,7 +5739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
         <v>76</v>
       </c>
@@ -5872,7 +5752,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
         <v>77</v>
       </c>
@@ -5885,7 +5765,7 @@
         <v>1.9825803230683253E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
         <v>78</v>
       </c>
@@ -5898,7 +5778,7 @@
         <v>1.9825803233769129E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
         <v>79</v>
       </c>
@@ -5911,7 +5791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
         <v>124</v>
       </c>
@@ -5924,7 +5804,7 @@
         <v>欣[test_cashflows.xlsx]CappedFlooredIborCoupon!R44C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
         <v>80</v>
       </c>
@@ -5937,7 +5817,7 @@
         <v>1.0290039283366714</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
         <v>81</v>
       </c>
@@ -5950,7 +5830,7 @@
         <v>欣[test_cashflows.xlsx]CappedFlooredIborCoupon!R46C3InterestRateIndex,A</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>85</v>
       </c>
@@ -5963,7 +5843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
         <v>86</v>
       </c>
@@ -5976,7 +5856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
         <v>87</v>
       </c>
@@ -5989,7 +5869,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="24" t="s">
         <v>88</v>
       </c>
@@ -6002,7 +5882,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
         <v>89</v>
       </c>
@@ -6015,7 +5895,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="24" t="s">
         <v>90</v>
       </c>
@@ -6036,14 +5916,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821189FD-C8F8-4090-B2E1-04E499EEED39}">
   <dimension ref="A1:C62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="91.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="91.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>125</v>
       </c>
@@ -6051,7 +5931,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -6060,7 +5940,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>111</v>
       </c>
@@ -6071,7 +5951,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>16</v>
       </c>
@@ -6082,7 +5962,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>112</v>
       </c>
@@ -6093,7 +5973,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>113</v>
       </c>
@@ -6104,7 +5984,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>124</v>
       </c>
@@ -6117,7 +5997,7 @@
         <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R8C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>134</v>
       </c>
@@ -6130,7 +6010,7 @@
         <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R9C3Estr,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>116</v>
       </c>
@@ -6139,7 +6019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>117</v>
       </c>
@@ -6148,7 +6028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>118</v>
       </c>
@@ -6157,7 +6037,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>119</v>
       </c>
@@ -6166,7 +6046,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>120</v>
       </c>
@@ -6175,7 +6055,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>135</v>
       </c>
@@ -6184,7 +6064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>136</v>
       </c>
@@ -6193,7 +6073,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>137</v>
       </c>
@@ -6202,7 +6082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>138</v>
       </c>
@@ -6211,7 +6091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>139</v>
       </c>
@@ -6220,7 +6100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>140</v>
       </c>
@@ -6229,7 +6109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>141</v>
       </c>
@@ -6238,7 +6118,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>142</v>
       </c>
@@ -6247,7 +6127,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
         <v>29</v>
       </c>
@@ -6260,7 +6140,7 @@
         <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R23C3OvernightIndexedCoupon,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>133</v>
       </c>
@@ -6270,7 +6150,7 @@
         <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R24C3OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
         <v>144</v>
       </c>
@@ -6283,7 +6163,7 @@
         <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R25C3BlackCompoundingOvernightIndexedCouponPricer,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
         <v>132</v>
       </c>
@@ -6296,7 +6176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
         <v>61</v>
       </c>
@@ -6309,7 +6189,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
         <v>62</v>
       </c>
@@ -6322,7 +6202,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>63</v>
       </c>
@@ -6335,7 +6215,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
         <v>64</v>
       </c>
@@ -6348,7 +6228,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>65</v>
       </c>
@@ -6361,7 +6241,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
         <v>66</v>
       </c>
@@ -6374,7 +6254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
         <v>67</v>
       </c>
@@ -6387,7 +6267,7 @@
         <v>2.0100058364902508E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
         <v>68</v>
       </c>
@@ -6400,7 +6280,7 @@
         <v>0.49863013698630138</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
         <v>69</v>
       </c>
@@ -6413,7 +6293,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
         <v>70</v>
       </c>
@@ -6426,7 +6306,7 @@
         <v>Actual/365 (Fixed)</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>71</v>
       </c>
@@ -6439,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
         <v>72</v>
       </c>
@@ -6452,7 +6332,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
         <v>73</v>
       </c>
@@ -6465,7 +6345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
         <v>129</v>
       </c>
@@ -6478,7 +6358,7 @@
         <v>PRECEDING</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
         <v>74</v>
       </c>
@@ -6491,7 +6371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
         <v>75</v>
       </c>
@@ -6504,7 +6384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
         <v>76</v>
       </c>
@@ -6517,7 +6397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
         <v>77</v>
       </c>
@@ -6530,7 +6410,7 @@
         <v>1.9726567846172216E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
         <v>78</v>
       </c>
@@ -6543,7 +6423,7 @@
         <v>2.0100058364902508E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
         <v>79</v>
       </c>
@@ -6556,7 +6436,7 @@
         <v>3.7349051873029199E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="30" t="s">
         <v>124</v>
       </c>
@@ -6569,7 +6449,7 @@
         <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R47C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
         <v>80</v>
       </c>
@@ -6582,7 +6462,7 @@
         <v>0.99230412262784928</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="24" t="s">
         <v>81</v>
       </c>
@@ -6595,7 +6475,7 @@
         <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R49C3InterestRateIndex,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
         <v>91</v>
       </c>
@@ -6608,7 +6488,7 @@
         <v>COMPOUND</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
         <v>92</v>
       </c>
@@ -6621,7 +6501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
         <v>93</v>
       </c>
@@ -6634,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
         <v>94</v>
       </c>
@@ -6647,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
         <v>95</v>
       </c>
@@ -6660,7 +6540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
         <v>96</v>
       </c>
@@ -6673,7 +6553,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
         <v>97</v>
       </c>
@@ -6686,7 +6566,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
         <v>98</v>
       </c>
@@ -6699,7 +6579,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
         <v>99</v>
       </c>
@@ -6712,7 +6592,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
         <v>100</v>
       </c>
@@ -6725,7 +6605,7 @@
         <v>2.7777777777777779E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
         <v>101</v>
       </c>
@@ -6738,7 +6618,7 @@
         <v>1.9726567846252152E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="24" t="s">
         <v>102</v>
       </c>
@@ -6751,7 +6631,7 @@
         <v>2.0100058364902508E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
         <v>103</v>
       </c>
@@ -6772,14 +6652,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39FC8A5-9394-4EB7-BCAE-447F9DD17ABC}">
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="73" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>125</v>
       </c>
@@ -6787,7 +6667,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -6796,7 +6676,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>111</v>
       </c>
@@ -6807,7 +6687,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>16</v>
       </c>
@@ -6818,7 +6698,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>112</v>
       </c>
@@ -6829,7 +6709,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>113</v>
       </c>
@@ -6840,7 +6720,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>114</v>
       </c>
@@ -6851,7 +6731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>124</v>
       </c>
@@ -6864,7 +6744,7 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R9C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>146</v>
       </c>
@@ -6877,7 +6757,7 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R10C3Euribor,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>145</v>
       </c>
@@ -6890,7 +6770,7 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R11C3SwapIndex,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>157</v>
       </c>
@@ -6901,7 +6781,7 @@
         <v>45288</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
         <v>158</v>
       </c>
@@ -6912,7 +6792,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
         <v>167</v>
       </c>
@@ -6925,7 +6805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>116</v>
       </c>
@@ -6934,7 +6814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>117</v>
       </c>
@@ -6943,7 +6823,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>118</v>
       </c>
@@ -6952,7 +6832,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>119</v>
       </c>
@@ -6961,7 +6841,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>120</v>
       </c>
@@ -6970,7 +6850,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>121</v>
       </c>
@@ -6979,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>130</v>
       </c>
@@ -6988,7 +6868,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>123</v>
       </c>
@@ -6997,7 +6877,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
         <v>147</v>
       </c>
@@ -7010,7 +6890,7 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R23C3CmsCoupon,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>153</v>
       </c>
@@ -7023,7 +6903,7 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R24C3SwaptionVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>154</v>
       </c>
@@ -7034,7 +6914,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
         <v>155</v>
       </c>
@@ -7045,7 +6925,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
         <v>159</v>
       </c>
@@ -7058,7 +6938,7 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R27C3AnalyticHaganPricer,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
         <v>132</v>
       </c>
@@ -7071,7 +6951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>61</v>
       </c>
@@ -7084,7 +6964,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
         <v>62</v>
       </c>
@@ -7097,7 +6977,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>63</v>
       </c>
@@ -7110,7 +6990,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
         <v>64</v>
       </c>
@@ -7123,7 +7003,7 @@
         <v>45293</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
         <v>65</v>
       </c>
@@ -7136,7 +7016,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
         <v>66</v>
       </c>
@@ -7149,7 +7029,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
         <v>67</v>
       </c>
@@ -7162,7 +7042,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
         <v>68</v>
       </c>
@@ -7175,7 +7055,7 @@
         <v>0.49863013698630138</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>69</v>
       </c>
@@ -7188,7 +7068,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
         <v>70</v>
       </c>
@@ -7201,7 +7081,7 @@
         <v>Actual/365 (Fixed)</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
         <v>71</v>
       </c>
@@ -7214,7 +7094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
         <v>72</v>
       </c>
@@ -7227,7 +7107,7 @@
         <v>45288</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
         <v>73</v>
       </c>
@@ -7240,7 +7120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
         <v>129</v>
       </c>
@@ -7253,7 +7133,7 @@
         <v>FOLLOWING</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
         <v>74</v>
       </c>
@@ -7266,7 +7146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
         <v>75</v>
       </c>
@@ -7279,7 +7159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
         <v>76</v>
       </c>
@@ -7292,7 +7172,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
         <v>77</v>
       </c>
@@ -7305,7 +7185,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>78</v>
       </c>
@@ -7318,7 +7198,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
         <v>79</v>
       </c>
@@ -7331,7 +7211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
         <v>124</v>
       </c>
@@ -7344,7 +7224,7 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R49C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
         <v>80</v>
       </c>
@@ -7357,7 +7237,7 @@
         <v>1.0367326401186752</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
         <v>81</v>
       </c>
@@ -7370,17 +7250,17 @@
         <v>欣[test_cashflows.xlsx]CmsCoupon!R51C3InterestRateIndex,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="37" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="38" t="s">
         <v>166</v>
       </c>

--- a/tests/workbooktests/workbooks/test_cashflows.xlsx
+++ b/tests/workbooktests/workbooks/test_cashflows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7570770-E35F-4B87-A01B-C898BEECD867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869345F8-22DF-4600-A534-FC09840F5081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4560" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="26" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="214">
   <si>
     <t>evaluationDate</t>
   </si>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t>=qlCashFlowsNpvBps(B20#;B4;WAHR)</t>
+  </si>
+  <si>
+    <t>rounding_precision</t>
   </si>
 </sst>
 </file>
@@ -4546,7 +4549,7 @@
       </c>
       <c r="B18" t="str">
         <f t="array" ref="B18">_xll.qlMakeSchedule(B13,B14,B15,,B12,B16)</f>
-        <v>欣[test_cashflows.xlsx]Legs!R18C2Schedule,C</v>
+        <v>欣[test_cashflows.xlsx]Legs!R18C2Schedule,A</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -5915,12 +5918,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821189FD-C8F8-4090-B2E1-04E499EEED39}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="91.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6128,519 +6131,537 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="13" t="str">
-        <f>_xll.qlOvernightIndexedCoupon(B4,B5,B6,B7,B9,,,,,,,,,,,,,B9)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R23C2OvernightIndexedCoupon,A</v>
-      </c>
-      <c r="C23" s="14" t="str">
-        <f>_xll.qlOvernightIndexedCoupon(C4,C5,C6,C7,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C9)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R23C3OvernightIndexedCoupon,A</v>
+      <c r="A23" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="22">
+        <v>45463</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11" t="str">
-        <f>_xll.qlConstantOptionletVolatility($B$1,"TARGET","ModifiedFollowing",0.2,"actual360",,,C23)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R24C3OptionletVolatilityStructureHandle,A</v>
+      <c r="A24" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="22">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="13" t="str">
+        <f>_xll.qlOvernightIndexedCoupon(B4,B5,B6,B7,B9,,,,,,,,,,,,,B9)</f>
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R25C2OvernightIndexedCoupon,A</v>
+      </c>
+      <c r="C25" s="14" t="str">
+        <f>_xll.qlOvernightIndexedCoupon(C4,C5,C6,C7,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23,C24,C9)</f>
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R25C3OvernightIndexedCoupon,A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11" t="str">
+        <f>_xll.qlConstantOptionletVolatility($B$1,"TARGET","ModifiedFollowing",0.2,"actual360",,,C25)</f>
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R26C3OptionletVolatilityStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="13" t="str">
+      <c r="B27" s="13" t="str">
         <f>_xll.qlBlackCompoundingOvernightIndexedCouponPricer()</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R25C2BlackCompoundingOvernightIndexedCouponPricer,A</v>
-      </c>
-      <c r="C25" s="14" t="str">
-        <f>_xll.qlBlackCompoundingOvernightIndexedCouponPricer(C24)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R25C3BlackCompoundingOvernightIndexedCouponPricer,A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R27C2BlackCompoundingOvernightIndexedCouponPricer,A</v>
+      </c>
+      <c r="C27" s="14" t="str">
+        <f>_xll.qlBlackCompoundingOvernightIndexedCouponPricer(C26)</f>
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R27C3BlackCompoundingOvernightIndexedCouponPricer,A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="13" t="b">
-        <f>_xll.qlFloatingRateCouponSetPricer(B23,B25)</f>
+      <c r="B28" s="13" t="b">
+        <f>_xll.qlFloatingRateCouponSetPricer(B25,B27)</f>
         <v>1</v>
       </c>
-      <c r="C26" s="14" t="b">
-        <f>_xll.qlFloatingRateCouponSetPricer(C23,C25)</f>
+      <c r="C28" s="14" t="b">
+        <f>_xll.qlFloatingRateCouponSetPricer(C25,C27)</f>
         <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="19">
-        <f>_xll.qlCouponNominal(B23,B26)</f>
-        <v>100</v>
-      </c>
-      <c r="C27" s="20">
-        <f>_xll.qlCouponNominal(C23,C26)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="25">
-        <f>_xll.qlCouponAccrualStartDate(B23,B26)</f>
-        <v>45293</v>
-      </c>
-      <c r="C28" s="26">
-        <f>_xll.qlCouponAccrualStartDate(C23,C26)</f>
-        <v>45293</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="21">
-        <f>_xll.qlCouponAccrualEndDate(B23,B26)</f>
-        <v>45475</v>
-      </c>
-      <c r="C29" s="22">
-        <f>_xll.qlCouponAccrualEndDate(C23,C26)</f>
-        <v>45475</v>
+        <v>61</v>
+      </c>
+      <c r="B29" s="19">
+        <f>_xll.qlCouponNominal(B25,B28)</f>
+        <v>100</v>
+      </c>
+      <c r="C29" s="20">
+        <f>_xll.qlCouponNominal(C25,C28)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B30" s="25">
-        <f>_xll.qlCouponReferencePeriodStart(B23,B26)</f>
+        <f>_xll.qlCouponAccrualStartDate(B25,B28)</f>
         <v>45293</v>
       </c>
       <c r="C30" s="26">
-        <f>_xll.qlCouponReferencePeriodStart(C23,C26)</f>
+        <f>_xll.qlCouponAccrualStartDate(C25,C28)</f>
         <v>45293</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B31" s="21">
-        <f>_xll.qlCouponReferencePeriodEnd(B23,B26)</f>
+        <f>_xll.qlCouponAccrualEndDate(B25,B28)</f>
         <v>45475</v>
       </c>
       <c r="C31" s="22">
-        <f>_xll.qlCouponReferencePeriodEnd(C23,C26)</f>
+        <f>_xll.qlCouponAccrualEndDate(C25,C28)</f>
         <v>45475</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="27">
-        <f>_xll.qlCouponExCouponDate(B23,B26)</f>
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="B32" s="25">
+        <f>_xll.qlCouponReferencePeriodStart(B25,B28)</f>
+        <v>45293</v>
       </c>
       <c r="C32" s="26">
-        <f>_xll.qlCouponExCouponDate(C23,C26)</f>
-        <v>0</v>
+        <f>_xll.qlCouponReferencePeriodStart(C25,C28)</f>
+        <v>45293</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="19">
-        <f>_xll.qlCouponRate(B23,B26)</f>
-        <v>1.9824715099629873E-2</v>
-      </c>
-      <c r="C33" s="20">
-        <f>_xll.qlCouponRate(C23,C26)</f>
-        <v>2.0100058364902508E-2</v>
+        <v>65</v>
+      </c>
+      <c r="B33" s="21">
+        <f>_xll.qlCouponReferencePeriodEnd(B25,B28)</f>
+        <v>45475</v>
+      </c>
+      <c r="C33" s="22">
+        <f>_xll.qlCouponReferencePeriodEnd(C25,C28)</f>
+        <v>45475</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B34" s="27">
-        <f>_xll.qlCouponAccrualPeriod(B23,B26)</f>
-        <v>0.50555555555555554</v>
-      </c>
-      <c r="C34" s="28">
-        <f>_xll.qlCouponAccrualPeriod(C23,C26)</f>
-        <v>0.49863013698630138</v>
+        <f>_xll.qlCouponExCouponDate(B25,B28)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="26">
+        <f>_xll.qlCouponExCouponDate(C25,C28)</f>
+        <v>45463</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B35" s="19">
-        <f>_xll.qlCouponAccrualDays(B23,B26)</f>
-        <v>182</v>
+        <f>_xll.qlCouponRate(B25,B28)</f>
+        <v>1.9824715099629873E-2</v>
       </c>
       <c r="C35" s="20">
-        <f>_xll.qlCouponAccrualDays(C23,C26)</f>
-        <v>182</v>
+        <f>_xll.qlCouponRate(C25,C28)</f>
+        <v>1.9824715099629873E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="27" t="str">
-        <f>_xll.qlCouponDayCounter(B23,B26)</f>
-        <v>Actual/360</v>
-      </c>
-      <c r="C36" s="28" t="str">
-        <f>_xll.qlCouponDayCounter(C23,C26)</f>
-        <v>Actual/365 (Fixed)</v>
+        <v>68</v>
+      </c>
+      <c r="B36" s="27">
+        <f>_xll.qlCouponAccrualPeriod(B25,B28)</f>
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="C36" s="28">
+        <f>_xll.qlCouponAccrualPeriod(C25,C28)</f>
+        <v>0.49863013698630138</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" s="19">
-        <f>_xll.qlCouponAccruedAmount(B23,"01.10.2024",B26)</f>
-        <v>0</v>
+        <f>_xll.qlCouponAccrualDays(B25,B28)</f>
+        <v>182</v>
       </c>
       <c r="C37" s="20">
-        <f>_xll.qlCouponAccruedAmount(C23,"01.10.2024",C26)</f>
-        <v>0</v>
+        <f>_xll.qlCouponAccrualDays(C25,C28)</f>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="25">
-        <f>_xll.qlFloatingRateCouponFixingDate(B23,B26)</f>
-        <v>45474</v>
-      </c>
-      <c r="C38" s="26">
-        <f>_xll.qlFloatingRateCouponFixingDate(C23,C26)</f>
-        <v>45474</v>
+        <v>70</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>_xll.qlCouponDayCounter(B25,B28)</f>
+        <v>Actual/360</v>
+      </c>
+      <c r="C38" s="28" t="str">
+        <f>_xll.qlCouponDayCounter(C25,C28)</f>
+        <v>Actual/365 (Fixed)</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B39" s="19">
-        <f>_xll.qlFloatingRateCouponFixingDays(B23,B26)</f>
+        <f>_xll.qlCouponAccruedAmount(B25,"01.10.2024",B28)</f>
         <v>0</v>
       </c>
       <c r="C39" s="20">
-        <f>_xll.qlFloatingRateCouponFixingDays(C23,C26)</f>
+        <f>_xll.qlCouponAccruedAmount(C25,"01.10.2024",C28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B40" s="27" t="str">
-        <f>_xll.qlFloatingRateCouponFixingConvention(B23,B26)</f>
-        <v>PRECEDING</v>
-      </c>
-      <c r="C40" s="28" t="str">
-        <f>_xll.qlFloatingRateCouponFixingConvention(C23,C26)</f>
-        <v>PRECEDING</v>
+        <v>72</v>
+      </c>
+      <c r="B40" s="25">
+        <f>_xll.qlFloatingRateCouponFixingDate(B25,B28)</f>
+        <v>45474</v>
+      </c>
+      <c r="C40" s="26">
+        <f>_xll.qlFloatingRateCouponFixingDate(C25,C28)</f>
+        <v>45474</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" s="19" t="b">
-        <f>_xll.qlFloatingRateCouponIsInArrears(B23,B26)</f>
-        <v>0</v>
-      </c>
-      <c r="C41" s="20" t="b">
-        <f>_xll.qlFloatingRateCouponIsInArrears(C23,C26)</f>
+        <v>73</v>
+      </c>
+      <c r="B41" s="19">
+        <f>_xll.qlFloatingRateCouponFixingDays(B25,B28)</f>
+        <v>0</v>
+      </c>
+      <c r="C41" s="20">
+        <f>_xll.qlFloatingRateCouponFixingDays(C25,C28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="27">
-        <f>_xll.qlFloatingRateCouponGearing(B23,B26)</f>
-        <v>1</v>
-      </c>
-      <c r="C42" s="28">
-        <f>_xll.qlFloatingRateCouponGearing(C23,C26)</f>
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>_xll.qlFloatingRateCouponFixingConvention(B25,B28)</f>
+        <v>PRECEDING</v>
+      </c>
+      <c r="C42" s="28" t="str">
+        <f>_xll.qlFloatingRateCouponFixingConvention(C25,C28)</f>
+        <v>PRECEDING</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="B43" s="19">
-        <f>_xll.qlFloatingRateCouponSpread(B23,B26)</f>
-        <v>0</v>
-      </c>
-      <c r="C43" s="20">
-        <f>_xll.qlFloatingRateCouponSpread(C23,C26)</f>
+        <v>74</v>
+      </c>
+      <c r="B43" s="19" t="b">
+        <f>_xll.qlFloatingRateCouponIsInArrears(B25,B28)</f>
+        <v>0</v>
+      </c>
+      <c r="C43" s="20" t="b">
+        <f>_xll.qlFloatingRateCouponIsInArrears(C25,C28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B44" s="27">
-        <f>_xll.qlFloatingRateCouponIndexFixing(B23,B26)</f>
-        <v>1.9726567846172216E-2</v>
+        <f>_xll.qlFloatingRateCouponGearing(B25,B28)</f>
+        <v>1</v>
       </c>
       <c r="C44" s="28">
-        <f>_xll.qlFloatingRateCouponIndexFixing(C23,C26)</f>
-        <v>1.9726567846172216E-2</v>
+        <f>_xll.qlFloatingRateCouponGearing(C25,C28)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B45" s="19">
-        <f>_xll.qlFloatingRateCouponAdjustedFixing(B23,B26)</f>
-        <v>1.9824715099629873E-2</v>
+        <f>_xll.qlFloatingRateCouponSpread(B25,B28)</f>
+        <v>0</v>
       </c>
       <c r="C45" s="20">
-        <f>_xll.qlFloatingRateCouponAdjustedFixing(C23,C26)</f>
-        <v>2.0100058364902508E-2</v>
+        <f>_xll.qlFloatingRateCouponSpread(C25,C28)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="27">
+        <f>_xll.qlFloatingRateCouponIndexFixing(B25,B28)</f>
+        <v>1.9726567846172216E-2</v>
+      </c>
+      <c r="C46" s="28">
+        <f>_xll.qlFloatingRateCouponIndexFixing(C25,C28)</f>
+        <v>1.9726567846172216E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="19">
+        <f>_xll.qlFloatingRateCouponAdjustedFixing(B25,B28)</f>
+        <v>1.9824715099629873E-2</v>
+      </c>
+      <c r="C47" s="20">
+        <f>_xll.qlFloatingRateCouponAdjustedFixing(C25,C28)</f>
+        <v>1.9824715099629873E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B46" s="27">
-        <f>_xll.qlFloatingRateCouponConvexityAdjustment(B23,B26)</f>
+      <c r="B48" s="27">
+        <f>_xll.qlFloatingRateCouponConvexityAdjustment(B25,B28)</f>
         <v>9.8147253457657457E-5</v>
       </c>
-      <c r="C46" s="28">
-        <f>_xll.qlFloatingRateCouponConvexityAdjustment(C23,C26)</f>
-        <v>3.7349051873029199E-4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
+      <c r="C48" s="28">
+        <f>_xll.qlFloatingRateCouponConvexityAdjustment(C25,C28)</f>
+        <v>9.8147253457657457E-5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="B47" s="19" t="str">
+      <c r="B49" s="19" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,B2)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R47C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C47" s="20" t="str">
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R49C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C49" s="20" t="str">
         <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed",,,C2)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R47C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="19">
-        <f>_xll.qlFloatingRateCouponPrice(B23,B47,B26)</f>
-        <v>0.99230412262784928</v>
-      </c>
-      <c r="C48" s="20">
-        <f>_xll.qlFloatingRateCouponPrice(C23,C47,C26)</f>
-        <v>0.99230412262784928</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49" s="27" t="str">
-        <f>_xll.qlFloatingRateCouponIndex(B23,B26)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R49C2InterestRateIndex,A</v>
-      </c>
-      <c r="C49" s="28" t="str">
-        <f>_xll.qlFloatingRateCouponIndex(C23,C26)</f>
-        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R49C3InterestRateIndex,A</v>
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R49C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="19" t="str">
-        <f>_xll.qlOvernightIndexedCouponAveragingMethod(B23,B26)</f>
-        <v>COMPOUND</v>
-      </c>
-      <c r="C50" s="20" t="str">
-        <f>_xll.qlOvernightIndexedCouponAveragingMethod(C23,C26)</f>
-        <v>COMPOUND</v>
+        <v>80</v>
+      </c>
+      <c r="B50" s="19">
+        <f>_xll.qlFloatingRateCouponPrice(B25,B49,B28)</f>
+        <v>0.99230412262784928</v>
+      </c>
+      <c r="C50" s="20">
+        <f>_xll.qlFloatingRateCouponPrice(C25,C49,C28)</f>
+        <v>0.98736441916064277</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="27" t="b">
-        <f>_xll.qlOvernightIndexedCouponCanApplyTelescopicFormula(B23,B25)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="28" t="b">
-        <f>_xll.qlOvernightIndexedCouponCanApplyTelescopicFormula(C23,C25)</f>
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="B51" s="27" t="str">
+        <f>_xll.qlFloatingRateCouponIndex(B25,B28)</f>
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R51C2InterestRateIndex,A</v>
+      </c>
+      <c r="C51" s="28" t="str">
+        <f>_xll.qlFloatingRateCouponIndex(C25,C28)</f>
+        <v>欣[test_cashflows.xlsx]OvernightIndexedCoupon!R51C3InterestRateIndex,A</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B52" s="19" t="b">
-        <f>_xll.qlOvernightIndexedCouponApplyObservationShift(B23,B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C52" s="20" t="b">
-        <f>_xll.qlOvernightIndexedCouponApplyObservationShift(C23,C25)</f>
-        <v>0</v>
+        <v>91</v>
+      </c>
+      <c r="B52" s="19" t="str">
+        <f>_xll.qlOvernightIndexedCouponAveragingMethod(B25,B28)</f>
+        <v>COMPOUND</v>
+      </c>
+      <c r="C52" s="20" t="str">
+        <f>_xll.qlOvernightIndexedCouponAveragingMethod(C25,C28)</f>
+        <v>COMPOUND</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B53" s="27" t="b">
-        <f>_xll.qlOvernightIndexedCouponCompoundSpreadDaily(B23,B25)</f>
-        <v>0</v>
+        <f>_xll.qlOvernightIndexedCouponCanApplyTelescopicFormula(B25,B27)</f>
+        <v>1</v>
       </c>
       <c r="C53" s="28" t="b">
-        <f>_xll.qlOvernightIndexedCouponCompoundSpreadDaily(C23,C25)</f>
-        <v>0</v>
+        <f>_xll.qlOvernightIndexedCouponCanApplyTelescopicFormula(C25,C27)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B54" s="19">
-        <f>_xll.qlOvernightIndexedCouponLockoutDays(B23,B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C54" s="20">
-        <f>_xll.qlOvernightIndexedCouponLockoutDays(C23,C25)</f>
+        <v>93</v>
+      </c>
+      <c r="B54" s="19" t="b">
+        <f>_xll.qlOvernightIndexedCouponApplyObservationShift(B25,B27)</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="20" t="b">
+        <f>_xll.qlOvernightIndexedCouponApplyObservationShift(C25,C27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="25">
-        <f>_xll.qlOvernightIndexedCouponRateComputationStartDate(B23,B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C55" s="26">
-        <f>_xll.qlOvernightIndexedCouponRateComputationStartDate(C23,C25)</f>
-        <v>45293</v>
+        <v>94</v>
+      </c>
+      <c r="B55" s="27" t="b">
+        <f>_xll.qlOvernightIndexedCouponCompoundSpreadDaily(B25,B27)</f>
+        <v>0</v>
+      </c>
+      <c r="C55" s="28" t="b">
+        <f>_xll.qlOvernightIndexedCouponCompoundSpreadDaily(C25,C27)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="21">
-        <f>_xll.qlOvernightIndexedCouponRateComputationEndDate(B23,B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C56" s="22">
-        <f>_xll.qlOvernightIndexedCouponRateComputationEndDate(C23,C25)</f>
-        <v>45475</v>
+        <v>95</v>
+      </c>
+      <c r="B56" s="19">
+        <f>_xll.qlOvernightIndexedCouponLockoutDays(B25,B27)</f>
+        <v>0</v>
+      </c>
+      <c r="C56" s="20">
+        <f>_xll.qlOvernightIndexedCouponLockoutDays(C25,C27)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B57" s="25">
-        <f>_xll.qlOvernightIndexedCouponValueDates(B23,B25)</f>
-        <v>45293</v>
+        <f>_xll.qlOvernightIndexedCouponRateComputationStartDate(B25,B27)</f>
+        <v>0</v>
       </c>
       <c r="C57" s="26">
-        <f>_xll.qlOvernightIndexedCouponValueDates(C23,C25)</f>
+        <f>_xll.qlOvernightIndexedCouponRateComputationStartDate(C25,C27)</f>
         <v>45293</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B58" s="21">
-        <f>_xll.qlOvernightIndexedCouponFixingDates(B23,B25)</f>
-        <v>45293</v>
+        <f>_xll.qlOvernightIndexedCouponRateComputationEndDate(B25,B27)</f>
+        <v>0</v>
       </c>
       <c r="C58" s="22">
-        <f>_xll.qlOvernightIndexedCouponFixingDates(C23,C25)</f>
-        <v>45293</v>
+        <f>_xll.qlOvernightIndexedCouponRateComputationEndDate(C25,C27)</f>
+        <v>45475</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B59" s="27">
-        <f>_xll.qlOvernightIndexedCouponDt(B23,B25)</f>
-        <v>2.7777777777777779E-3</v>
-      </c>
-      <c r="C59" s="28">
-        <f>_xll.qlOvernightIndexedCouponDt(C23,C25)</f>
-        <v>2.7777777777777779E-3</v>
+        <v>98</v>
+      </c>
+      <c r="B59" s="25">
+        <f>_xll.qlOvernightIndexedCouponValueDates(B25,B27)</f>
+        <v>45293</v>
+      </c>
+      <c r="C59" s="26">
+        <f>_xll.qlOvernightIndexedCouponValueDates(C25,C27)</f>
+        <v>45293</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="B60" s="19">
-        <f>_xll.qlOvernightIndexedCouponIndexFixings(B23,B25)</f>
-        <v>1.9726567846252152E-2</v>
-      </c>
-      <c r="C60" s="20">
-        <f>_xll.qlOvernightIndexedCouponIndexFixings(C23,C25)</f>
-        <v>1.9726567846252152E-2</v>
+        <v>99</v>
+      </c>
+      <c r="B60" s="21">
+        <f>_xll.qlOvernightIndexedCouponFixingDates(B25,B27)</f>
+        <v>45293</v>
+      </c>
+      <c r="C60" s="22">
+        <f>_xll.qlOvernightIndexedCouponFixingDates(C25,C27)</f>
+        <v>45293</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B61" s="27">
+        <f>_xll.qlOvernightIndexedCouponDt(B25,B27)</f>
+        <v>2.7777777777777779E-3</v>
+      </c>
+      <c r="C61" s="28">
+        <f>_xll.qlOvernightIndexedCouponDt(C25,C27)</f>
+        <v>2.7777777777777779E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B62" s="19">
+        <f>_xll.qlOvernightIndexedCouponIndexFixings(B25,B27)</f>
+        <v>1.9726567846252152E-2</v>
+      </c>
+      <c r="C62" s="20">
+        <f>_xll.qlOvernightIndexedCouponIndexFixings(C25,C27)</f>
+        <v>1.9726567846252152E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B61" s="27">
-        <f>_xll.qlOvernightIndexedCouponEffectiveIndexFixing(B23,B25)</f>
+      <c r="B63" s="27">
+        <f>_xll.qlOvernightIndexedCouponEffectiveIndexFixing(B25,B27)</f>
         <v>1.9824715099629873E-2</v>
       </c>
-      <c r="C61" s="28">
-        <f>_xll.qlOvernightIndexedCouponEffectiveIndexFixing(C23,C25)</f>
-        <v>2.0100058364902508E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="23" t="s">
+      <c r="C63" s="28">
+        <f>_xll.qlOvernightIndexedCouponEffectiveIndexFixing(C25,C27)</f>
+        <v>1.9824715099629873E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B62" s="13">
-        <f>_xll.qlOvernightIndexedCouponEffectiveSpread(B23,B25)</f>
-        <v>0</v>
-      </c>
-      <c r="C62" s="14">
-        <f>_xll.qlOvernightIndexedCouponEffectiveSpread(C23,C25)</f>
+      <c r="B64" s="13">
+        <f>_xll.qlOvernightIndexedCouponEffectiveSpread(B25,B27)</f>
+        <v>0</v>
+      </c>
+      <c r="C64" s="14">
+        <f>_xll.qlOvernightIndexedCouponEffectiveSpread(C25,C27)</f>
         <v>0</v>
       </c>
     </row>
